--- a/TASTI_SYNTHETIC/PnoTGB.xlsx
+++ b/TASTI_SYNTHETIC/PnoTGB.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>41U842C151</t>
+          <t>33X522S648</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,19 +443,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>52U604V741</t>
+          <t>97W575P162</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55D23L</t>
+          <t>NS60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>72N148E767</t>
+          <t>90Z603Z817</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>37T405A708</t>
+          <t>81D707Q543</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
